--- a/reports/cashier-pdf-reports_cache_report:III.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:III.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>386</x:v>
+        <x:v>436</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>2290</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2043,7 +2043,7 @@
       <x:c r="N18" s="56" t="s"/>
       <x:c r="O18" s="58" t="s"/>
       <x:c r="P18" s="60" t="n">
-        <x:v>302</x:v>
+        <x:v>352</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:16">
@@ -2091,7 +2091,7 @@
       <x:c r="N20" s="56" t="s"/>
       <x:c r="O20" s="58" t="s"/>
       <x:c r="P20" s="60" t="n">
-        <x:v>3361</x:v>
+        <x:v>3841</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>28261</x:v>
+        <x:v>35761</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>2290</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2279,7 +2279,7 @@
       <x:c r="N28" s="56" t="s"/>
       <x:c r="O28" s="58" t="s"/>
       <x:c r="P28" s="60" t="n">
-        <x:v>18750</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:16">
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>2321</x:v>
+        <x:v>2721</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2371,7 +2371,7 @@
       <x:c r="N32" s="56" t="s"/>
       <x:c r="O32" s="58" t="s"/>
       <x:c r="P32" s="76" t="n">
-        <x:v>21</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:16">
@@ -2395,7 +2395,7 @@
       <x:c r="N33" s="56" t="s"/>
       <x:c r="O33" s="58" t="s"/>
       <x:c r="P33" s="76" t="n">
-        <x:v>21</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:16">
@@ -2557,7 +2557,7 @@
       <x:c r="N40" s="56" t="s"/>
       <x:c r="O40" s="58" t="s"/>
       <x:c r="P40" s="60" t="n">
-        <x:v>351</x:v>
+        <x:v>651</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>781</x:v>
+        <x:v>1081</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>68366</x:v>
+        <x:v>86256</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:III.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:III.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>3300</x:v>
+        <x:v>3800</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>35761</x:v>
+        <x:v>37261</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>3300</x:v>
+        <x:v>3800</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>1081</x:v>
+        <x:v>1111</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>86256</x:v>
+        <x:v>88786</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:III.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:III.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>436</x:v>
+        <x:v>386</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>3800</x:v>
+        <x:v>2790</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2043,7 +2043,7 @@
       <x:c r="N18" s="56" t="s"/>
       <x:c r="O18" s="58" t="s"/>
       <x:c r="P18" s="60" t="n">
-        <x:v>352</x:v>
+        <x:v>302</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:16">
@@ -2091,7 +2091,7 @@
       <x:c r="N20" s="56" t="s"/>
       <x:c r="O20" s="58" t="s"/>
       <x:c r="P20" s="60" t="n">
-        <x:v>3841</x:v>
+        <x:v>3361</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>37261</x:v>
+        <x:v>29761</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>3800</x:v>
+        <x:v>2790</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2279,7 +2279,7 @@
       <x:c r="N28" s="56" t="s"/>
       <x:c r="O28" s="58" t="s"/>
       <x:c r="P28" s="60" t="n">
-        <x:v>25500</x:v>
+        <x:v>18750</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:16">
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>2721</x:v>
+        <x:v>2321</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2371,7 +2371,7 @@
       <x:c r="N32" s="56" t="s"/>
       <x:c r="O32" s="58" t="s"/>
       <x:c r="P32" s="76" t="n">
-        <x:v>41</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:16">
@@ -2395,7 +2395,7 @@
       <x:c r="N33" s="56" t="s"/>
       <x:c r="O33" s="58" t="s"/>
       <x:c r="P33" s="76" t="n">
-        <x:v>41</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:16">
@@ -2557,7 +2557,7 @@
       <x:c r="N40" s="56" t="s"/>
       <x:c r="O40" s="58" t="s"/>
       <x:c r="P40" s="60" t="n">
-        <x:v>651</x:v>
+        <x:v>351</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>1111</x:v>
+        <x:v>811</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>88786</x:v>
+        <x:v>70896</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:III.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:III.xlsx
@@ -2323,7 +2323,7 @@
       <x:c r="N30" s="56" t="s"/>
       <x:c r="O30" s="58" t="s"/>
       <x:c r="P30" s="60" t="n">
-        <x:v>6216</x:v>
+        <x:v>6360</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:16">
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>2321</x:v>
+        <x:v>2381</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>811</x:v>
+        <x:v>841</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>70896</x:v>
+        <x:v>71130</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:III.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:III.xlsx
@@ -1995,7 +1995,7 @@
       <x:c r="N16" s="56" t="s"/>
       <x:c r="O16" s="58" t="s"/>
       <x:c r="P16" s="60" t="n">
-        <x:v>386</x:v>
+        <x:v>578</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:16">
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>2790</x:v>
+        <x:v>3150</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>2790</x:v>
+        <x:v>3150</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2323,7 +2323,7 @@
       <x:c r="N30" s="56" t="s"/>
       <x:c r="O30" s="58" t="s"/>
       <x:c r="P30" s="60" t="n">
-        <x:v>6360</x:v>
+        <x:v>6504</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:16">
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>2381</x:v>
+        <x:v>3461</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>841</x:v>
+        <x:v>871</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>71130</x:v>
+        <x:v>73296</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:III.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:III.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>29761</x:v>
+        <x:v>31261</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2279,7 +2279,7 @@
       <x:c r="N28" s="56" t="s"/>
       <x:c r="O28" s="58" t="s"/>
       <x:c r="P28" s="60" t="n">
-        <x:v>18750</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>871</x:v>
+        <x:v>901</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>73296</x:v>
+        <x:v>56076</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:III.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:III.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>31261</x:v>
+        <x:v>33421</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>901</x:v>
+        <x:v>931</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>56076</x:v>
+        <x:v>58266</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:III.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:III.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>33421</x:v>
+        <x:v>34141</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>931</x:v>
+        <x:v>961</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>58266</x:v>
+        <x:v>59016</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:III.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:III.xlsx
@@ -2347,7 +2347,7 @@
       <x:c r="N31" s="56" t="s"/>
       <x:c r="O31" s="58" t="s"/>
       <x:c r="P31" s="76" t="n">
-        <x:v>3461</x:v>
+        <x:v>3761</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>961</x:v>
+        <x:v>991</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>59016</x:v>
+        <x:v>59346</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:III.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:III.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>34141</x:v>
+        <x:v>35641</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>991</x:v>
+        <x:v>1021</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>59346</x:v>
+        <x:v>60876</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:III.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:III.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>3150</x:v>
+        <x:v>3650</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>35641</x:v>
+        <x:v>37141</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>3150</x:v>
+        <x:v>3650</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>1021</x:v>
+        <x:v>1051</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>60876</x:v>
+        <x:v>63406</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:III.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:III.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>3650</x:v>
+        <x:v>4150</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>37141</x:v>
+        <x:v>38641</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>3650</x:v>
+        <x:v>4150</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>1051</x:v>
+        <x:v>1081</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>63406</x:v>
+        <x:v>65936</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:III.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:III.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>4150</x:v>
+        <x:v>4650</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>38641</x:v>
+        <x:v>40141</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>4150</x:v>
+        <x:v>4650</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>1081</x:v>
+        <x:v>1111</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>65936</x:v>
+        <x:v>68466</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:III.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:III.xlsx
@@ -2019,7 +2019,7 @@
       <x:c r="N17" s="56" t="s"/>
       <x:c r="O17" s="58" t="s"/>
       <x:c r="P17" s="60" t="n">
-        <x:v>4650</x:v>
+        <x:v>5150</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:16">
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>40141</x:v>
+        <x:v>41641</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2255,7 +2255,7 @@
       <x:c r="N27" s="56" t="s"/>
       <x:c r="O27" s="58" t="s"/>
       <x:c r="P27" s="60" t="n">
-        <x:v>4650</x:v>
+        <x:v>5150</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>1111</x:v>
+        <x:v>1141</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>68466</x:v>
+        <x:v>70996</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">

--- a/reports/cashier-pdf-reports_cache_report:III.xlsx
+++ b/reports/cashier-pdf-reports_cache_report:III.xlsx
@@ -2115,7 +2115,7 @@
       <x:c r="N21" s="56" t="s"/>
       <x:c r="O21" s="58" t="s"/>
       <x:c r="P21" s="60" t="n">
-        <x:v>41641</x:v>
+        <x:v>43141</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:16">
@@ -2653,7 +2653,7 @@
       <x:c r="N44" s="56" t="s"/>
       <x:c r="O44" s="58" t="s"/>
       <x:c r="P44" s="76" t="n">
-        <x:v>1141</x:v>
+        <x:v>1171</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:16">
@@ -2675,7 +2675,7 @@
       <x:c r="N45" s="56" t="s"/>
       <x:c r="O45" s="58" t="s"/>
       <x:c r="P45" s="76" t="n">
-        <x:v>70996</x:v>
+        <x:v>72526</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:16">
